--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_61992.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_61992.xlsx
@@ -745,6 +745,9 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_61992.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_61992.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cccd</t>
+          <t>Iviuic irl i</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>POUDSC</t>
+          <t>PLOLUSISLILE IIRL</t>
         </is>
       </c>
     </row>
